--- a/04반.xlsx
+++ b/04반.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>수행실2</t>
+          <t>수행실1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>수행실2</t>
+          <t>자습</t>
         </is>
       </c>
     </row>

--- a/04반.xlsx
+++ b/04반.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>수행실2</t>
+          <t>학원 자습</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>수행실2</t>
+          <t>학원 자습</t>
         </is>
       </c>
     </row>

--- a/04반.xlsx
+++ b/04반.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>학원 자습</t>
+          <t>자습실1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>학원 자습</t>
+          <t>자습</t>
         </is>
       </c>
     </row>
